--- a/web/files/九龙-九龙塘-The Monet 第3期.xlsx
+++ b/web/files/九龙-九龙塘-The Monet 第3期.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
@@ -4131,7 +4131,7 @@
           <t>B | 0呎 (null房)
 $11990万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -4154,7 +4154,7 @@
           <t>A | 0呎 (null房)
 $9790万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
@@ -4170,7 +4170,7 @@
           <t>C | 0呎 (null房)
 $7070万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
           <t>B | 0呎 (null房)
 $10500万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -4216,7 +4216,7 @@
           <t>A | 0呎 (null房)
 $9690万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
@@ -4232,7 +4232,7 @@
           <t>C | 0呎 (null房)
 $7000万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
           <t>B | 0呎 (null房)
 $10290万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -4278,7 +4278,7 @@
           <t>A | 0呎 (null房)
 $9510万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -4294,7 +4294,7 @@
           <t>C | 0呎 (null房)
 $6870万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
           <t>B | 0呎 (null房)
 $10190万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -4340,7 +4340,7 @@
           <t>A | 0呎 (null房)
 $9410万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
@@ -4356,7 +4356,7 @@
           <t>C | 0呎 (null房)
 $6800万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
           <t>B | 0呎 (null房)
 $10090万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -4402,7 +4402,7 @@
           <t>A | 0呎 (null房)
 $9320万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
@@ -4418,7 +4418,7 @@
           <t>C | 0呎 (null房)
 $6730万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
           <t>B | 0呎 (null房)
 $9990万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -4464,7 +4464,7 @@
           <t>A | 0呎 (null房)
 $9230万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
@@ -4480,7 +4480,7 @@
           <t>C | 0呎 (null房)
 $6660万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
           <t>B | 0呎 (null房)
 $9840万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -4526,7 +4526,7 @@
           <t>A | 0呎 (null房)
 $9090万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
@@ -4542,7 +4542,7 @@
           <t>C | 0呎 (null房)
 $6560万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
           <t>B | 0呎 (null房)
 $9520万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -4588,7 +4588,7 @@
           <t>A | 0呎 (null房)
 $9390万
 -
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr"/>
